--- a/jira_export_2026-09-04.xlsx
+++ b/jira_export_2026-09-04.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>74 h</t>
+          <t>84 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="11" t="inlineStr"/>
@@ -1686,12 +1686,12 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Mairie de Pontcharra] - Migration simple placier</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration simple placier</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1726,23 +1726,23 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
@@ -1758,12 +1758,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1798,29 +1798,29 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
@@ -1830,27 +1830,27 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
@@ -1870,21 +1870,29 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L16" s="14" t="inlineStr"/>
-      <c r="M16" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="inlineStr">
+        <is>
+          <t>00171691</t>
+        </is>
+      </c>
       <c r="N16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="15" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="O16" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="15" t="n">
@@ -1894,27 +1902,27 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1924,7 +1932,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -1941,22 +1949,14 @@
         <v>3</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M17" s="11" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L17" s="11" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr"/>
       <c r="N17" s="12" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="12" t="n">
@@ -1966,32 +1966,32 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>0</v>
@@ -2038,32 +2038,32 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2073,32 +2073,32 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2110,12 +2110,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
@@ -2157,20 +2157,20 @@
         <v>3</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2182,27 +2182,27 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2217,32 +2217,32 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2254,12 +2254,12 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
@@ -2305,16 +2305,16 @@
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>0</v>
@@ -2326,12 +2326,12 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
@@ -2377,16 +2377,16 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2398,27 +2398,27 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
@@ -2449,16 +2449,16 @@
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
@@ -2470,32 +2470,32 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -2505,32 +2505,32 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O25" s="16" t="n">
         <v>0</v>
@@ -2542,27 +2542,27 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2589,20 +2589,20 @@
         <v>3</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -2614,12 +2614,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2654,29 +2654,29 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="O27" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="12" t="n">
@@ -2686,12 +2686,12 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2733,22 +2733,22 @@
         <v>3</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P28" s="15" t="n">
@@ -2758,27 +2758,27 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2798,27 +2798,27 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2830,27 +2830,27 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2870,59 +2870,59 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>0.5</v>
+        <v>2.75</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="P30" s="15" t="n">
-        <v>1080</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>171.4</v>
+        <v>920</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2974,32 +2974,32 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -3014,59 +3014,59 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>344</v>
-      </c>
-      <c r="O32" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O32" s="15" t="n">
+        <v>540</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3086,29 +3086,29 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="O33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="12" t="n">
@@ -3118,32 +3118,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
@@ -3169,16 +3169,16 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>149</v>
+        <v>171.4</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3190,32 +3190,32 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3230,27 +3230,27 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>625</v>
+        <v>344</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3262,32 +3262,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3302,29 +3302,29 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="O36" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="15" t="n">
@@ -3334,12 +3334,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
@@ -3385,16 +3385,16 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>910</v>
+        <v>149</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3406,32 +3406,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3441,32 +3441,32 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>2</v>
+        <v>0.62</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>1207</v>
+        <v>625</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3478,12 +3478,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3518,29 +3518,29 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="O39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
@@ -3550,32 +3550,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3585,34 +3585,34 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="15" t="n">
+        <v>910</v>
+      </c>
+      <c r="O40" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="15" t="n">
@@ -3622,32 +3622,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>142.1</v>
+        <v>1207</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3694,32 +3694,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3729,32 +3729,32 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K42" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>2335</v>
+        <v>500</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3766,27 +3766,27 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3806,23 +3806,23 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K43" s="11" t="n">
         <v>0.25</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
@@ -3838,32 +3838,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3873,32 +3873,32 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K44" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>450</v>
+        <v>142.1</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3910,32 +3910,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3945,32 +3945,32 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>910</v>
+        <v>2335</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3982,32 +3982,32 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4017,34 +4017,34 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P46" s="15" t="n">
@@ -4054,12 +4054,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4105,16 +4105,16 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>285</v>
+        <v>450</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4166,27 +4166,27 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>1325</v>
+        <v>910</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4198,32 +4198,32 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4249,16 +4249,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>120</v>
+        <v>590.15</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4270,12 +4270,12 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4321,16 +4321,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>588</v>
+        <v>285</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4342,32 +4342,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4377,32 +4377,32 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>203.5</v>
+        <v>1325</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4414,32 +4414,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4449,32 +4449,32 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K52" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4486,32 +4486,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K53" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>700</v>
+        <v>588</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4558,27 +4558,27 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
@@ -4609,16 +4609,16 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>210</v>
+        <v>203.5</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4630,27 +4630,27 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
@@ -4681,16 +4681,16 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4702,32 +4702,32 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
@@ -4753,16 +4753,16 @@
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>255</v>
+        <v>700</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4774,12 +4774,12 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4814,27 +4814,27 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K57" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4846,32 +4846,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4881,32 +4881,32 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>690</v>
+        <v>130</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4918,32 +4918,32 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4953,32 +4953,32 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K59" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>187.5</v>
+        <v>255</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -4990,32 +4990,32 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
@@ -5041,16 +5041,16 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>787.5</v>
+        <v>140</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5062,32 +5062,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5097,35 +5097,35 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
-        <v>362.5</v>
+        <v>690</v>
+      </c>
+      <c r="O61" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
         <v>0</v>
@@ -5134,27 +5134,27 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5169,34 +5169,34 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="15" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="O62" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="15" t="n">
@@ -5206,27 +5206,27 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5241,34 +5241,34 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="12" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O63" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
@@ -5278,32 +5278,32 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -5313,35 +5313,35 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P64" s="15" t="n">
         <v>0</v>
@@ -5397,16 +5397,16 @@
         <v>10</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>1.05</v>
+        <v>0.85</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
@@ -5469,22 +5469,22 @@
         <v>10</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>1.05</v>
+        <v>0.85</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
@@ -5494,12 +5494,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5509,11 +5509,13 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
@@ -5527,28 +5529,28 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
@@ -5564,12 +5566,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
@@ -5579,34 +5581,50 @@
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>CD74</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="inlineStr"/>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H68" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L68" s="14" t="inlineStr"/>
-      <c r="M68" s="14" t="inlineStr"/>
+        <v>0.85</v>
+      </c>
+      <c r="L68" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28203</t>
+        </is>
+      </c>
+      <c r="M68" s="14" t="inlineStr">
+        <is>
+          <t>00144860</t>
+        </is>
+      </c>
       <c r="N68" s="15" t="n">
         <v>0</v>
       </c>
@@ -5620,12 +5638,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5635,11 +5653,13 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
@@ -5653,34 +5673,34 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.25</v>
+        <v>0.85</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O69" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5690,12 +5710,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5705,7 +5725,7 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E70" s="14" t="n">
@@ -5723,34 +5743,34 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O70" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="15" t="n">
@@ -5760,12 +5780,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5775,48 +5795,34 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F71" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H71" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr"/>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K71" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="L71" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28055</t>
-        </is>
-      </c>
-      <c r="M71" s="11" t="inlineStr">
-        <is>
-          <t>499132</t>
-        </is>
-      </c>
+      <c r="L71" s="11" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr"/>
       <c r="N71" s="12" t="n">
         <v>0</v>
       </c>
@@ -5830,12 +5836,12 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
@@ -5845,13 +5851,11 @@
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E72" s="14" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="n">
+        <v/>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
@@ -5860,7 +5864,7 @@
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H72" s="14" t="inlineStr">
@@ -5870,23 +5874,23 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K72" s="14" t="n">
         <v>0.25</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
@@ -5902,22 +5906,22 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -5935,32 +5939,32 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K73" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>401</v>
+        <v>1212</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5972,22 +5976,22 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E74" s="14" t="n">
@@ -6010,23 +6014,23 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
@@ -6042,26 +6046,28 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
@@ -6070,7 +6076,7 @@
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
@@ -6080,29 +6086,29 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O75" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -6112,22 +6118,22 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E76" s="14" t="n">
@@ -6145,34 +6151,34 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O76" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6182,22 +6188,22 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
@@ -6220,23 +6226,23 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.25</v>
+        <v>3.25</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
@@ -6252,22 +6258,22 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E78" s="14" t="n">
@@ -6280,7 +6286,7 @@
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H78" s="14" t="inlineStr">
@@ -6290,21 +6296,29 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L78" s="14" t="inlineStr"/>
-      <c r="M78" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L78" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M78" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N78" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6314,22 +6328,22 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -6342,7 +6356,7 @@
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
@@ -6352,17 +6366,25 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L79" s="11" t="inlineStr"/>
-      <c r="M79" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28215</t>
+        </is>
+      </c>
+      <c r="M79" s="11" t="inlineStr">
+        <is>
+          <t>458306</t>
+        </is>
+      </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
       </c>
@@ -6376,22 +6398,22 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E80" s="14" t="n">
@@ -6399,7 +6421,7 @@
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6409,34 +6431,34 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28214</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>458286</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6446,22 +6468,22 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -6474,7 +6496,7 @@
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
@@ -6484,29 +6506,21 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>21</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M81" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L81" s="11" t="inlineStr"/>
+      <c r="M81" s="11" t="inlineStr"/>
       <c r="N81" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O81" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6516,22 +6530,22 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E82" s="14" t="n">
@@ -6554,14 +6568,14 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L82" s="14" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -6578,22 +6592,22 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -6601,7 +6615,7 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6611,34 +6625,34 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O83" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6648,22 +6662,22 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E84" s="14" t="n">
@@ -6676,27 +6690,39 @@
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H84" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H84" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L84" s="14" t="inlineStr"/>
-      <c r="M84" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L84" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M84" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N84" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O84" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
@@ -6706,24 +6732,26 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C85" s="11" t="inlineStr"/>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v/>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
@@ -6742,14 +6770,14 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>2.25</v>
+        <v>0.25</v>
       </c>
       <c r="L85" s="11" t="inlineStr"/>
       <c r="M85" s="11" t="inlineStr"/>
@@ -6764,31 +6792,219 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="17" t="inlineStr">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12747</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H86" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>26/09/2023</t>
+        </is>
+      </c>
+      <c r="J86" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K86" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L86" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M86" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N86" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12708</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr"/>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+      <c r="J87" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K87" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L87" s="11" t="inlineStr"/>
+      <c r="M87" s="11" t="inlineStr"/>
+      <c r="N87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr"/>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J88" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K88" s="14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L88" s="14" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+      <c r="N88" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B86" s="17" t="inlineStr"/>
-      <c r="C86" s="17" t="inlineStr"/>
-      <c r="D86" s="17" t="inlineStr"/>
-      <c r="E86" s="17" t="inlineStr"/>
-      <c r="F86" s="17" t="inlineStr"/>
-      <c r="G86" s="17" t="inlineStr"/>
-      <c r="H86" s="17" t="inlineStr"/>
-      <c r="I86" s="17" t="inlineStr"/>
-      <c r="J86" s="17" t="inlineStr"/>
-      <c r="K86" s="17" t="inlineStr"/>
-      <c r="L86" s="17" t="inlineStr"/>
-      <c r="M86" s="17" t="inlineStr"/>
-      <c r="N86" s="18" t="n">
+      <c r="B89" s="17" t="inlineStr"/>
+      <c r="C89" s="17" t="inlineStr"/>
+      <c r="D89" s="17" t="inlineStr"/>
+      <c r="E89" s="17" t="inlineStr"/>
+      <c r="F89" s="17" t="inlineStr"/>
+      <c r="G89" s="17" t="inlineStr"/>
+      <c r="H89" s="17" t="inlineStr"/>
+      <c r="I89" s="17" t="inlineStr"/>
+      <c r="J89" s="17" t="inlineStr"/>
+      <c r="K89" s="17" t="inlineStr"/>
+      <c r="L89" s="17" t="inlineStr"/>
+      <c r="M89" s="17" t="inlineStr"/>
+      <c r="N89" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O86" s="18" t="n">
+      <c r="O89" s="18" t="n">
         <v>1805.22</v>
       </c>
-      <c r="P86" s="18" t="n">
-        <v>41.99</v>
+      <c r="P89" s="18" t="n">
+        <v>33.75</v>
       </c>
     </row>
   </sheetData>
@@ -6875,6 +7091,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7524,16 +7743,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>23.25</v>
+        <v>28.25</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>33.5</v>
+        <v>40.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>3.5</v>
@@ -7543,7 +7762,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7773,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -7563,7 +7782,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>4</v>
@@ -7573,7 +7792,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
     </row>
@@ -7670,10 +7889,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>368554</v>
+        <v>369009</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>128054</v>
+        <v>128509</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>240501</v>
@@ -7695,10 +7914,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>166814</v>
+        <v>167269</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>63707</v>
+        <v>64162</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>103107</v>
@@ -7749,13 +7968,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -7773,7 +7992,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 3 commande(s)</t>
+          <t>Épics créées ce mois — 5 commande(s)</t>
         </is>
       </c>
     </row>
@@ -7828,22 +8047,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -7863,22 +8082,22 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -7888,7 +8107,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -7908,104 +8127,152 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-35392</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35385</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE ROUEN</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>00179700</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35460</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-35439</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-35435</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>00180506</t>
         </is>
       </c>
-      <c r="I7" s="25" t="n">
-        <v>3974</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>3 commande(s)</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="n">
-        <v>5174</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>dont Littéralis</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>1 commande(s)</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="n">
+      <c r="I9" s="25" t="n">
         <v>3974</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B10" s="17" t="n"/>
@@ -8016,10 +8283,52 @@
       <c r="G10" s="17" t="n"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
+          <t>5 commande(s)</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="n">
+        <v>5629</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>dont Littéralis</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
           <t>2 commande(s)</t>
         </is>
       </c>
-      <c r="I10" s="24" t="n">
+      <c r="I11" s="24" t="n">
+        <v>4429</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>3 commande(s)</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="n">
         <v>1200</v>
       </c>
     </row>

--- a/jira_export_2026-09-04.xlsx
+++ b/jira_export_2026-09-04.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>84 h</t>
+          <t>95 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L8" s="14" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
         <v>2</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>3</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>36</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>1805.22</v>
       </c>
       <c r="P89" s="18" t="n">
-        <v>33.75</v>
+        <v>31.82</v>
       </c>
     </row>
   </sheetData>
@@ -7743,26 +7743,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>28.25</v>
+        <v>30.25</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>7</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>40.5</v>
+        <v>42.75</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>652.05</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -7782,17 +7782,17 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>275.31</v>
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.7%</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>23.5</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-09-04.xlsx
+++ b/jira_export_2026-09-04.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>95 h</t>
+          <t>101 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P89"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2949,7 +2949,7 @@
         <v>3</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
@@ -5350,12 +5350,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5365,13 +5365,11 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v/>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
@@ -5390,23 +5388,23 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
@@ -5469,16 +5467,16 @@
         <v>10</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
@@ -5541,16 +5539,16 @@
         <v>10</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
@@ -5613,16 +5611,16 @@
         <v>10</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
@@ -5685,22 +5683,22 @@
         <v>10</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O69" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5710,12 +5708,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5725,11 +5723,13 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E70" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
@@ -5743,34 +5743,34 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="15" t="n">
@@ -5780,12 +5780,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5795,34 +5795,48 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F71" s="11" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H71" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" s="11" t="inlineStr"/>
-      <c r="M71" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
       </c>
@@ -5836,12 +5850,12 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
@@ -5851,48 +5865,34 @@
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E72" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F72" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr"/>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H72" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H72" s="14" t="inlineStr"/>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L72" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M72" s="14" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L72" s="14" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
       <c r="N72" s="15" t="n">
         <v>0</v>
       </c>
@@ -5906,12 +5906,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -5939,34 +5939,34 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O73" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -5976,12 +5976,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E74" s="14" t="n">
@@ -6014,29 +6014,29 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O74" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
@@ -6046,12 +6046,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6061,13 +6061,11 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v/>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
@@ -6076,33 +6074,33 @@
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>13</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
@@ -6118,26 +6116,28 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
-        </is>
-      </c>
-      <c r="E76" s="14" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H76" s="14" t="inlineStr">
@@ -6156,29 +6156,29 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6188,12 +6188,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
@@ -6221,34 +6221,34 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O77" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="12" t="n">
@@ -6258,12 +6258,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E78" s="14" t="n">
@@ -6291,34 +6291,34 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O78" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6328,22 +6328,22 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -6361,34 +6361,34 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O79" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
@@ -6443,16 +6443,16 @@
         <v>19</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
@@ -6468,12 +6468,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -6496,27 +6496,35 @@
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L81" s="11" t="inlineStr"/>
-      <c r="M81" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
       </c>
@@ -6530,22 +6538,22 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E82" s="14" t="n">
@@ -6563,7 +6571,7 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
@@ -6575,7 +6583,7 @@
         <v>21</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="L82" s="14" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -6592,22 +6600,22 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -6615,44 +6623,36 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>21</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M83" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr"/>
       <c r="N83" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O83" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6662,22 +6662,22 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E84" s="14" t="n">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
@@ -6711,16 +6711,16 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6732,22 +6732,22 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -6760,31 +6760,39 @@
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L85" s="11" t="inlineStr"/>
-      <c r="M85" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M85" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O85" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6794,22 +6802,22 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E86" s="14" t="n">
@@ -6822,35 +6830,27 @@
       </c>
       <c r="G86" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L86" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M86" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L86" s="14" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
       <c r="N86" s="15" t="n">
         <v>0</v>
       </c>
@@ -6864,22 +6864,22 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -6892,23 +6892,35 @@
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H87" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L87" s="11" t="inlineStr"/>
-      <c r="M87" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M87" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N87" s="12" t="n">
         <v>0</v>
       </c>
@@ -6922,24 +6934,26 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C88" s="14" t="inlineStr"/>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E88" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v/>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -6951,21 +6965,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H88" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H88" s="14" t="inlineStr"/>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="L88" s="14" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -6980,31 +6990,91 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="17" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr"/>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L89" s="11" t="inlineStr"/>
+      <c r="M89" s="11" t="inlineStr"/>
+      <c r="N89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B89" s="17" t="inlineStr"/>
-      <c r="C89" s="17" t="inlineStr"/>
-      <c r="D89" s="17" t="inlineStr"/>
-      <c r="E89" s="17" t="inlineStr"/>
-      <c r="F89" s="17" t="inlineStr"/>
-      <c r="G89" s="17" t="inlineStr"/>
-      <c r="H89" s="17" t="inlineStr"/>
-      <c r="I89" s="17" t="inlineStr"/>
-      <c r="J89" s="17" t="inlineStr"/>
-      <c r="K89" s="17" t="inlineStr"/>
-      <c r="L89" s="17" t="inlineStr"/>
-      <c r="M89" s="17" t="inlineStr"/>
-      <c r="N89" s="18" t="n">
+      <c r="B90" s="17" t="inlineStr"/>
+      <c r="C90" s="17" t="inlineStr"/>
+      <c r="D90" s="17" t="inlineStr"/>
+      <c r="E90" s="17" t="inlineStr"/>
+      <c r="F90" s="17" t="inlineStr"/>
+      <c r="G90" s="17" t="inlineStr"/>
+      <c r="H90" s="17" t="inlineStr"/>
+      <c r="I90" s="17" t="inlineStr"/>
+      <c r="J90" s="17" t="inlineStr"/>
+      <c r="K90" s="17" t="inlineStr"/>
+      <c r="L90" s="17" t="inlineStr"/>
+      <c r="M90" s="17" t="inlineStr"/>
+      <c r="N90" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O89" s="18" t="n">
+      <c r="O90" s="18" t="n">
         <v>1805.22</v>
       </c>
-      <c r="P89" s="18" t="n">
-        <v>31.82</v>
+      <c r="P90" s="18" t="n">
+        <v>29.6</v>
       </c>
     </row>
   </sheetData>
@@ -7094,6 +7164,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7743,16 +7814,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>30.25</v>
+        <v>32.5</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>5.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>42.75</v>
+        <v>47</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>5.5</v>
@@ -7762,7 +7833,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.2%</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7875,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>27</v>
+        <v>28.75</v>
       </c>
     </row>
   </sheetData>
